--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2</f>
+              <f>'OssDsign'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2</f>
+              <f>'OssDsign'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2</f>
+              <f>'OssDsign'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2</f>
+              <f>'OssDsign'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2</f>
+              <f>'Smart Eye'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2</f>
+              <f>'Smart Eye'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2</f>
+              <f>'Smart Eye'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2</f>
+              <f>'Smart Eye'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2</f>
+              <f>'Integrum'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2</f>
+              <f>'Integrum'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2</f>
+              <f>'Integrum'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2</f>
+              <f>'Integrum'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1030,6 +1030,23 @@
       </c>
       <c r="D2" s="2">
         <f>B2+C2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2941</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3+C3</f>
         <v/>
       </c>
     </row>
@@ -1045,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1090,6 +1107,23 @@
       </c>
       <c r="D2" s="2">
         <f>B2+C2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>11743</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>7025</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3+C3</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1153,6 +1187,23 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2493</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3+C3</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$3</f>
+              <f>'OssDsign'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$3</f>
+              <f>'OssDsign'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$3</f>
+              <f>'OssDsign'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$3</f>
+              <f>'OssDsign'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$3</f>
+              <f>'Smart Eye'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$3</f>
+              <f>'Smart Eye'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$3</f>
+              <f>'Smart Eye'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$3</f>
+              <f>'Smart Eye'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$3</f>
+              <f>'Integrum'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$3</f>
+              <f>'Integrum'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$3</f>
+              <f>'Integrum'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$3</f>
+              <f>'Integrum'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1047,6 +1047,23 @@
       </c>
       <c r="D3" s="2">
         <f>B3+C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2937</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4+C4</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1124,6 +1141,23 @@
       </c>
       <c r="D3" s="2">
         <f>B3+C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>11723</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>7034</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4+C4</f>
         <v/>
       </c>
     </row>
@@ -1139,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1204,6 +1238,23 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4+C4</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D4" s="2">
         <f>B4+C4</f>
@@ -1154,7 +1154,7 @@
         <v>11723</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7034</v>
+        <v>7043</v>
       </c>
       <c r="D4" s="2">
         <f>B4+C4</f>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>567</v>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$4</f>
+              <f>'OssDsign'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$4</f>
+              <f>'OssDsign'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$4</f>
+              <f>'OssDsign'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$4</f>
+              <f>'OssDsign'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$4</f>
+              <f>'Smart Eye'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$4</f>
+              <f>'Smart Eye'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$4</f>
+              <f>'Smart Eye'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$4</f>
+              <f>'Smart Eye'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$4</f>
+              <f>'Integrum'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$4</f>
+              <f>'Integrum'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$4</f>
+              <f>'Integrum'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$4</f>
+              <f>'Integrum'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1064,6 +1064,23 @@
       </c>
       <c r="D4" s="2">
         <f>B4+C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2937</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5+C5</f>
         <v/>
       </c>
     </row>
@@ -1079,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1158,6 +1175,23 @@
       </c>
       <c r="D4" s="2">
         <f>B4+C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>11709</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>7043</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5+C5</f>
         <v/>
       </c>
     </row>
@@ -1173,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1255,6 +1289,23 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5+C5</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
